--- a/기획/직업별 능력치_250515.xlsx
+++ b/기획/직업별 능력치_250515.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\typar\Desktop\storage\기획\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{030CCCA6-6386-4C47-971B-C94DA33D0A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B8F978-293D-4572-9B0E-5F2C8FB3CBCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -155,9 +155,6 @@
     <t>무작위 출혈 단일 공격</t>
   </si>
   <si>
-    <t>30-(30-방어력)/100</t>
-  </si>
-  <si>
     <t>아군 전체 데미지 증가</t>
   </si>
   <si>
@@ -351,6 +348,10 @@
   </si>
   <si>
     <t>최고 체력</t>
+  </si>
+  <si>
+    <t>30-(30*방어력)/100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -360,7 +361,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -369,6 +370,13 @@
     <font>
       <sz val="8"/>
       <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -496,7 +504,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -533,12 +541,6 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -546,6 +548,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -905,51 +916,51 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B2:AH51"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.9140625" customWidth="1"/>
-    <col min="3" max="10" width="10.58203125" customWidth="1"/>
-    <col min="11" max="11" width="26.4140625" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="10" width="10.625" customWidth="1"/>
+    <col min="11" max="11" width="26.375" customWidth="1"/>
     <col min="12" max="12" width="26" customWidth="1"/>
-    <col min="13" max="13" width="11.9140625" customWidth="1"/>
-    <col min="14" max="23" width="10.58203125" customWidth="1"/>
-    <col min="24" max="24" width="9.58203125" customWidth="1"/>
+    <col min="13" max="13" width="11.875" customWidth="1"/>
+    <col min="14" max="23" width="10.625" customWidth="1"/>
+    <col min="24" max="24" width="9.625" customWidth="1"/>
     <col min="25" max="25" width="9.5" customWidth="1"/>
-    <col min="26" max="26" width="13.6640625" customWidth="1"/>
-    <col min="27" max="27" width="8.6640625" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="28.58203125" customWidth="1"/>
+    <col min="26" max="26" width="13.625" customWidth="1"/>
+    <col min="27" max="27" width="8.625" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="28.625" customWidth="1"/>
     <col min="29" max="29" width="32" customWidth="1"/>
-    <col min="30" max="30" width="24.4140625" customWidth="1"/>
+    <col min="30" max="30" width="24.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:29" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="K3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="K4" t="s">
         <v>84</v>
       </c>
-      <c r="H2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="K3" t="s">
+    </row>
+    <row r="5" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="K5" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="4" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="K4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="2:29" x14ac:dyDescent="0.45">
-      <c r="K5" t="s">
-        <v>87</v>
-      </c>
-      <c r="X5" s="13" t="s">
+      <c r="X5" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="Y5" s="13"/>
-      <c r="Z5" s="13"/>
-      <c r="AA5" s="13"/>
+      <c r="Y5" s="15"/>
+      <c r="Z5" s="15"/>
+      <c r="AA5" s="15"/>
       <c r="AB5" s="1" t="s">
         <v>13</v>
       </c>
@@ -957,48 +968,48 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:29" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:29" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" t="s">
+        <v>66</v>
+      </c>
+      <c r="G6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" t="s">
         <v>45</v>
-      </c>
-      <c r="E6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F6" t="s">
-        <v>67</v>
-      </c>
-      <c r="G6" t="s">
-        <v>48</v>
-      </c>
-      <c r="H6" t="s">
-        <v>46</v>
       </c>
       <c r="M6" s="1"/>
       <c r="N6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R6" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
-      <c r="X6" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y6" s="13"/>
-      <c r="Z6" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="AA6" s="13"/>
+      <c r="X6" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="Y6" s="15"/>
+      <c r="Z6" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA6" s="15"/>
       <c r="AB6" s="1" t="s">
         <v>18</v>
       </c>
@@ -1006,68 +1017,68 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="2:29" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:29" x14ac:dyDescent="0.3">
       <c r="C7" s="2"/>
       <c r="D7" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M7" s="2"/>
       <c r="N7" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="V7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="X7" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y7" s="13"/>
-      <c r="Z7" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA7" s="13"/>
+      <c r="X7" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y7" s="15"/>
+      <c r="Z7" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA7" s="15"/>
       <c r="AC7" s="1"/>
     </row>
-    <row r="8" spans="2:29" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="2" t="s">
         <v>3</v>
       </c>
@@ -1128,16 +1139,16 @@
         <f>U8-(N24*2)</f>
         <v>74</v>
       </c>
-      <c r="X8" s="13">
+      <c r="X8" s="15">
         <f t="shared" ref="X8:X19" si="1">30-(30*O8)/100</f>
         <v>26.4</v>
       </c>
-      <c r="Y8" s="13"/>
-      <c r="Z8" s="13">
+      <c r="Y8" s="15"/>
+      <c r="Z8" s="15">
         <f t="shared" ref="Z8:Z19" si="2">30-P8</f>
         <v>15</v>
       </c>
-      <c r="AA8" s="13"/>
+      <c r="AA8" s="15"/>
       <c r="AB8" s="1">
         <f t="shared" ref="AB8:AB19" si="3">95-Q8*3</f>
         <v>92</v>
@@ -1147,7 +1158,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="2:29" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C9" s="2" t="s">
         <v>8</v>
       </c>
@@ -1208,16 +1219,16 @@
         <f>U9-(N24*2)</f>
         <v>79</v>
       </c>
-      <c r="X9" s="13">
+      <c r="X9" s="15">
         <f t="shared" si="1"/>
         <v>28.2</v>
       </c>
-      <c r="Y9" s="13"/>
-      <c r="Z9" s="13">
+      <c r="Y9" s="15"/>
+      <c r="Z9" s="15">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="AA9" s="13"/>
+      <c r="AA9" s="15"/>
       <c r="AB9" s="1">
         <f t="shared" si="3"/>
         <v>89</v>
@@ -1227,7 +1238,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="2:29" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="2" t="s">
         <v>1</v>
       </c>
@@ -1288,16 +1299,16 @@
         <f>U10-(N24*2)</f>
         <v>65</v>
       </c>
-      <c r="X10" s="13">
+      <c r="X10" s="15">
         <f t="shared" si="1"/>
         <v>28.8</v>
       </c>
-      <c r="Y10" s="13"/>
-      <c r="Z10" s="13">
+      <c r="Y10" s="15"/>
+      <c r="Z10" s="15">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="AA10" s="13"/>
+      <c r="AA10" s="15"/>
       <c r="AB10" s="1">
         <f t="shared" si="3"/>
         <v>74</v>
@@ -1307,7 +1318,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="2:29" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="2" t="s">
         <v>4</v>
       </c>
@@ -1368,16 +1379,16 @@
         <f>U11-(N24*2)</f>
         <v>71</v>
       </c>
-      <c r="X11" s="13">
+      <c r="X11" s="15">
         <f t="shared" si="1"/>
         <v>25.5</v>
       </c>
-      <c r="Y11" s="13"/>
-      <c r="Z11" s="13">
+      <c r="Y11" s="15"/>
+      <c r="Z11" s="15">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="AA11" s="13"/>
+      <c r="AA11" s="15"/>
       <c r="AB11" s="1">
         <f t="shared" si="3"/>
         <v>80</v>
@@ -1387,7 +1398,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="2:29" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="2" t="s">
         <v>6</v>
       </c>
@@ -1448,16 +1459,16 @@
         <f>U12-(N24*2)</f>
         <v>55</v>
       </c>
-      <c r="X12" s="13">
+      <c r="X12" s="15">
         <f t="shared" si="1"/>
         <v>28.8</v>
       </c>
-      <c r="Y12" s="13"/>
-      <c r="Z12" s="13">
+      <c r="Y12" s="15"/>
+      <c r="Z12" s="15">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="AA12" s="13"/>
+      <c r="AA12" s="15"/>
       <c r="AB12" s="1">
         <f t="shared" si="3"/>
         <v>71</v>
@@ -1467,7 +1478,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="2:29" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C13" s="2" t="s">
         <v>10</v>
       </c>
@@ -1528,16 +1539,16 @@
         <f>U13-(N24*2)</f>
         <v>59</v>
       </c>
-      <c r="X13" s="13">
+      <c r="X13" s="15">
         <f t="shared" si="1"/>
         <v>27.9</v>
       </c>
-      <c r="Y13" s="13"/>
-      <c r="Z13" s="13">
+      <c r="Y13" s="15"/>
+      <c r="Z13" s="15">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="AA13" s="13"/>
+      <c r="AA13" s="15"/>
       <c r="AB13" s="1">
         <f t="shared" si="3"/>
         <v>77</v>
@@ -1547,7 +1558,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="2:29" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C14" s="2" t="s">
         <v>5</v>
       </c>
@@ -1608,16 +1619,16 @@
         <f>U14-(N24*2)</f>
         <v>51</v>
       </c>
-      <c r="X14" s="13">
+      <c r="X14" s="15">
         <f t="shared" si="1"/>
         <v>29.1</v>
       </c>
-      <c r="Y14" s="13"/>
-      <c r="Z14" s="13">
+      <c r="Y14" s="15"/>
+      <c r="Z14" s="15">
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="AA14" s="13"/>
+      <c r="AA14" s="15"/>
       <c r="AB14" s="1">
         <f t="shared" si="3"/>
         <v>86</v>
@@ -1627,7 +1638,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="2:29" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C15" s="2" t="s">
         <v>11</v>
       </c>
@@ -1688,16 +1699,16 @@
         <f>U15-(N24*2)</f>
         <v>60</v>
       </c>
-      <c r="X15" s="13">
+      <c r="X15" s="15">
         <f t="shared" si="1"/>
         <v>29.1</v>
       </c>
-      <c r="Y15" s="13"/>
-      <c r="Z15" s="13">
+      <c r="Y15" s="15"/>
+      <c r="Z15" s="15">
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="AA15" s="13"/>
+      <c r="AA15" s="15"/>
       <c r="AB15" s="1">
         <f t="shared" si="3"/>
         <v>83</v>
@@ -1707,7 +1718,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="2:29" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C16" s="2" t="s">
         <v>7</v>
       </c>
@@ -1768,16 +1779,16 @@
         <f>U16-(N24*2)</f>
         <v>61</v>
       </c>
-      <c r="X16" s="13">
+      <c r="X16" s="15">
         <f t="shared" si="1"/>
         <v>28.5</v>
       </c>
-      <c r="Y16" s="13"/>
-      <c r="Z16" s="13">
+      <c r="Y16" s="15"/>
+      <c r="Z16" s="15">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="AA16" s="13"/>
+      <c r="AA16" s="15"/>
       <c r="AB16" s="1">
         <f t="shared" si="3"/>
         <v>86</v>
@@ -1787,7 +1798,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="2:34" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:34" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C17" s="2" t="s">
         <v>9</v>
       </c>
@@ -1848,16 +1859,16 @@
         <f>U17-(N24*2)</f>
         <v>57</v>
       </c>
-      <c r="X17" s="13">
+      <c r="X17" s="15">
         <f t="shared" si="1"/>
         <v>29.1</v>
       </c>
-      <c r="Y17" s="13"/>
-      <c r="Z17" s="13">
+      <c r="Y17" s="15"/>
+      <c r="Z17" s="15">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="AA17" s="13"/>
+      <c r="AA17" s="15"/>
       <c r="AB17" s="1">
         <f t="shared" si="3"/>
         <v>65</v>
@@ -1867,7 +1878,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="2:34" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:34" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C18" s="2" t="s">
         <v>2</v>
       </c>
@@ -1928,16 +1939,16 @@
         <f>U18-(N24*2)</f>
         <v>44</v>
       </c>
-      <c r="X18" s="13">
+      <c r="X18" s="15">
         <f t="shared" si="1"/>
         <v>29.4</v>
       </c>
-      <c r="Y18" s="13"/>
-      <c r="Z18" s="13">
+      <c r="Y18" s="15"/>
+      <c r="Z18" s="15">
         <f t="shared" si="2"/>
         <v>26</v>
       </c>
-      <c r="AA18" s="13"/>
+      <c r="AA18" s="15"/>
       <c r="AB18" s="1">
         <f t="shared" si="3"/>
         <v>92</v>
@@ -1947,9 +1958,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="2:34" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:34" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C19" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D19" s="2">
         <v>1</v>
@@ -1975,7 +1986,7 @@
         <v>1.6</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N19" s="2">
         <v>42</v>
@@ -2008,16 +2019,16 @@
         <f>U19-(N24*2)</f>
         <v>49</v>
       </c>
-      <c r="X19" s="13">
+      <c r="X19" s="15">
         <f t="shared" si="1"/>
         <v>29.4</v>
       </c>
-      <c r="Y19" s="13"/>
-      <c r="Z19" s="13">
+      <c r="Y19" s="15"/>
+      <c r="Z19" s="15">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="AA19" s="13"/>
+      <c r="AA19" s="15"/>
       <c r="AB19" s="1">
         <f t="shared" si="3"/>
         <v>92</v>
@@ -2027,12 +2038,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="2:34" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:34" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D20" s="2">
         <f>SUM(D8:D19)</f>
@@ -2057,7 +2068,7 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="M20" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N20" s="2">
         <f>SUM(N8:N19)</f>
@@ -2084,9 +2095,9 @@
       <c r="U20" s="2"/>
       <c r="V20" s="2"/>
     </row>
-    <row r="21" spans="2:34" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:34" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C21" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D21" s="2">
         <f>ROUND(AVERAGE(D8:D19),1)</f>
@@ -2111,7 +2122,7 @@
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="M21" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N21" s="2">
         <f>ROUND(AVERAGE(N8:N19),1)</f>
@@ -2138,15 +2149,15 @@
       <c r="U21" s="2"/>
       <c r="V21" s="2"/>
     </row>
-    <row r="22" spans="2:34" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:34" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D22" s="4"/>
     </row>
-    <row r="23" spans="2:34" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:34" x14ac:dyDescent="0.3">
       <c r="L23" t="s">
         <v>36</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="N23" s="10">
         <v>5</v>
@@ -2165,9 +2176,9 @@
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
     </row>
-    <row r="24" spans="2:34" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:34" x14ac:dyDescent="0.3">
       <c r="M24" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N24" s="10">
         <v>4</v>
@@ -2186,7 +2197,7 @@
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
     </row>
-    <row r="25" spans="2:34" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:34" x14ac:dyDescent="0.3">
       <c r="M25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
@@ -2197,7 +2208,7 @@
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
     </row>
-    <row r="26" spans="2:34" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:34" x14ac:dyDescent="0.3">
       <c r="M26" s="1"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
@@ -2208,7 +2219,7 @@
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
     </row>
-    <row r="27" spans="2:34" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:34" x14ac:dyDescent="0.3">
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
@@ -2218,49 +2229,49 @@
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
     </row>
-    <row r="28" spans="2:34" ht="23" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:34" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C28" s="1"/>
       <c r="D28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L28" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="M28" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N28" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P28" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="O28" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="P28" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="Q28" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
@@ -2269,15 +2280,15 @@
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
     </row>
-    <row r="29" spans="2:34" ht="23" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:34" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>33</v>
       </c>
-      <c r="C29" s="12" t="s">
-        <v>55</v>
+      <c r="C29" s="16" t="s">
+        <v>54</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E29" s="2">
         <v>30</v>
@@ -2295,7 +2306,7 @@
         <v>100</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>21</v>
@@ -2303,23 +2314,23 @@
       <c r="L29" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="M29" s="14">
+      <c r="M29" s="12">
         <f>ROUND(AVERAGE(E29:E35),1)</f>
         <v>33.4</v>
       </c>
-      <c r="N29" s="14">
+      <c r="N29" s="12">
         <f>ROUND(AVERAGE(F29:F35),1)</f>
         <v>5</v>
       </c>
-      <c r="O29" s="14">
+      <c r="O29" s="12">
         <f>ROUND(AVERAGE(G29:G35),1)</f>
         <v>2.1</v>
       </c>
-      <c r="P29" s="14">
+      <c r="P29" s="12">
         <f>ROUND(AVERAGE(H29:H35),1)</f>
         <v>4.4000000000000004</v>
       </c>
-      <c r="Q29" s="14">
+      <c r="Q29" s="12">
         <f>ROUND(AVERAGE(I29:I35),1)</f>
         <v>95</v>
       </c>
@@ -2329,20 +2340,20 @@
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
-      <c r="AG29" s="13" t="s">
-        <v>73</v>
+      <c r="AG29" s="15" t="s">
+        <v>72</v>
       </c>
       <c r="AH29" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="2:34" ht="23" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:34" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>100</v>
-      </c>
-      <c r="C30" s="12"/>
+        <v>99</v>
+      </c>
+      <c r="C30" s="16"/>
       <c r="D30" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E30" s="2">
         <v>25</v>
@@ -2360,35 +2371,35 @@
         <v>100</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L30" s="2"/>
-      <c r="M30" s="15"/>
-      <c r="N30" s="15"/>
-      <c r="O30" s="15"/>
-      <c r="P30" s="15"/>
-      <c r="Q30" s="15"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13"/>
+      <c r="P30" s="13"/>
+      <c r="Q30" s="13"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
-      <c r="AG30" s="13"/>
+      <c r="AG30" s="15"/>
       <c r="AH30" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="31" spans="2:34" ht="23" customHeight="1" x14ac:dyDescent="0.45">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="31" spans="2:34" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>101</v>
-      </c>
-      <c r="C31" s="12"/>
+        <v>100</v>
+      </c>
+      <c r="C31" s="16"/>
       <c r="D31" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E31" s="2">
         <v>42</v>
@@ -2406,17 +2417,17 @@
         <v>90</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>27</v>
       </c>
       <c r="L31" s="2"/>
-      <c r="M31" s="15"/>
-      <c r="N31" s="15"/>
-      <c r="O31" s="15"/>
-      <c r="P31" s="15"/>
-      <c r="Q31" s="15"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13"/>
+      <c r="P31" s="13"/>
+      <c r="Q31" s="13"/>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
       <c r="T31" s="1"/>
@@ -2430,13 +2441,13 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="32" spans="2:34" ht="23" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:34" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="12"/>
+      <c r="C32" s="16"/>
       <c r="D32" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E32" s="6">
         <v>37</v>
@@ -2454,19 +2465,19 @@
         <v>85</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L32" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="M32" s="15"/>
-      <c r="N32" s="15"/>
-      <c r="O32" s="15"/>
-      <c r="P32" s="15"/>
-      <c r="Q32" s="15"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13"/>
+      <c r="P32" s="13"/>
+      <c r="Q32" s="13"/>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
       <c r="T32" s="1"/>
@@ -2474,13 +2485,13 @@
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
     </row>
-    <row r="33" spans="2:23" ht="23" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:23" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>99</v>
-      </c>
-      <c r="C33" s="12"/>
+        <v>98</v>
+      </c>
+      <c r="C33" s="16"/>
       <c r="D33" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E33" s="7">
         <v>30</v>
@@ -2498,17 +2509,17 @@
         <v>100</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K33" s="7" t="s">
         <v>39</v>
       </c>
       <c r="L33" s="7"/>
-      <c r="M33" s="15"/>
-      <c r="N33" s="15"/>
-      <c r="O33" s="15"/>
-      <c r="P33" s="15"/>
-      <c r="Q33" s="15"/>
+      <c r="M33" s="13"/>
+      <c r="N33" s="13"/>
+      <c r="O33" s="13"/>
+      <c r="P33" s="13"/>
+      <c r="Q33" s="13"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
@@ -2516,13 +2527,13 @@
       <c r="V33" s="1"/>
       <c r="W33" s="1"/>
     </row>
-    <row r="34" spans="2:23" ht="23" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:23" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>37</v>
       </c>
-      <c r="C34" s="12"/>
+      <c r="C34" s="16"/>
       <c r="D34" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E34" s="8">
         <v>25</v>
@@ -2540,17 +2551,17 @@
         <v>95</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K34" s="8" t="s">
         <v>35</v>
       </c>
       <c r="L34" s="8"/>
-      <c r="M34" s="15"/>
-      <c r="N34" s="15"/>
-      <c r="O34" s="15"/>
-      <c r="P34" s="15"/>
-      <c r="Q34" s="15"/>
+      <c r="M34" s="13"/>
+      <c r="N34" s="13"/>
+      <c r="O34" s="13"/>
+      <c r="P34" s="13"/>
+      <c r="Q34" s="13"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
@@ -2558,13 +2569,13 @@
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
     </row>
-    <row r="35" spans="2:23" ht="23" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:23" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>29</v>
       </c>
-      <c r="C35" s="12"/>
+      <c r="C35" s="16"/>
       <c r="D35" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E35" s="8">
         <v>45</v>
@@ -2582,19 +2593,19 @@
         <v>95</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L35" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="M35" s="16"/>
-      <c r="N35" s="16"/>
-      <c r="O35" s="16"/>
-      <c r="P35" s="16"/>
-      <c r="Q35" s="16"/>
+      <c r="M35" s="14"/>
+      <c r="N35" s="14"/>
+      <c r="O35" s="14"/>
+      <c r="P35" s="14"/>
+      <c r="Q35" s="14"/>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
       <c r="T35" s="1"/>
@@ -2602,15 +2613,15 @@
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
     </row>
-    <row r="36" spans="2:23" ht="23" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:23" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>30</v>
       </c>
-      <c r="C36" s="12" t="s">
-        <v>56</v>
+      <c r="C36" s="16" t="s">
+        <v>55</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E36" s="5">
         <v>55</v>
@@ -2628,7 +2639,7 @@
         <v>85</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K36" s="5" t="s">
         <v>25</v>
@@ -2636,23 +2647,23 @@
       <c r="L36" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="M36" s="14">
+      <c r="M36" s="12">
         <f>ROUND(AVERAGE(E36:E41),1)</f>
         <v>42.5</v>
       </c>
-      <c r="N36" s="14">
+      <c r="N36" s="12">
         <f t="shared" ref="N36:Q36" si="12">ROUND(AVERAGE(F36:F41),1)</f>
         <v>7.5</v>
       </c>
-      <c r="O36" s="14">
+      <c r="O36" s="12">
         <f t="shared" si="12"/>
         <v>4.2</v>
       </c>
-      <c r="P36" s="14">
+      <c r="P36" s="12">
         <f t="shared" si="12"/>
         <v>4.5</v>
       </c>
-      <c r="Q36" s="14">
+      <c r="Q36" s="12">
         <f t="shared" si="12"/>
         <v>95.8</v>
       </c>
@@ -2663,13 +2674,13 @@
       <c r="V36" s="1"/>
       <c r="W36" s="1"/>
     </row>
-    <row r="37" spans="2:23" ht="23" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:23" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>31</v>
       </c>
-      <c r="C37" s="12"/>
+      <c r="C37" s="16"/>
       <c r="D37" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E37" s="2">
         <v>42</v>
@@ -2687,7 +2698,7 @@
         <v>100</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>28</v>
@@ -2695,19 +2706,19 @@
       <c r="L37" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M37" s="15"/>
-      <c r="N37" s="15"/>
-      <c r="O37" s="15"/>
-      <c r="P37" s="15"/>
-      <c r="Q37" s="15"/>
-    </row>
-    <row r="38" spans="2:23" ht="23" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M37" s="13"/>
+      <c r="N37" s="13"/>
+      <c r="O37" s="13"/>
+      <c r="P37" s="13"/>
+      <c r="Q37" s="13"/>
+    </row>
+    <row r="38" spans="2:23" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>34</v>
       </c>
-      <c r="C38" s="12"/>
+      <c r="C38" s="16"/>
       <c r="D38" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E38" s="6">
         <v>35</v>
@@ -2725,7 +2736,7 @@
         <v>95</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>19</v>
@@ -2733,19 +2744,19 @@
       <c r="L38" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="M38" s="15"/>
-      <c r="N38" s="15"/>
-      <c r="O38" s="15"/>
-      <c r="P38" s="15"/>
-      <c r="Q38" s="15"/>
-    </row>
-    <row r="39" spans="2:23" ht="23" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M38" s="13"/>
+      <c r="N38" s="13"/>
+      <c r="O38" s="13"/>
+      <c r="P38" s="13"/>
+      <c r="Q38" s="13"/>
+    </row>
+    <row r="39" spans="2:23" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
-        <v>103</v>
-      </c>
-      <c r="C39" s="12"/>
+        <v>102</v>
+      </c>
+      <c r="C39" s="16"/>
       <c r="D39" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E39" s="8">
         <v>40</v>
@@ -2763,25 +2774,25 @@
         <v>100</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L39" s="8"/>
-      <c r="M39" s="15"/>
-      <c r="N39" s="15"/>
-      <c r="O39" s="15"/>
-      <c r="P39" s="15"/>
-      <c r="Q39" s="15"/>
-    </row>
-    <row r="40" spans="2:23" ht="23" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="M39" s="13"/>
+      <c r="N39" s="13"/>
+      <c r="O39" s="13"/>
+      <c r="P39" s="13"/>
+      <c r="Q39" s="13"/>
+    </row>
+    <row r="40" spans="2:23" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
-        <v>72</v>
-      </c>
-      <c r="C40" s="12"/>
+        <v>71</v>
+      </c>
+      <c r="C40" s="16"/>
       <c r="D40" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E40" s="5">
         <v>35</v>
@@ -2799,27 +2810,27 @@
         <v>105</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L40" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="M40" s="15"/>
-      <c r="N40" s="15"/>
-      <c r="O40" s="15"/>
-      <c r="P40" s="15"/>
-      <c r="Q40" s="15"/>
-    </row>
-    <row r="41" spans="2:23" ht="23" customHeight="1" x14ac:dyDescent="0.45">
+        <v>103</v>
+      </c>
+      <c r="M40" s="13"/>
+      <c r="N40" s="13"/>
+      <c r="O40" s="13"/>
+      <c r="P40" s="13"/>
+      <c r="Q40" s="13"/>
+    </row>
+    <row r="41" spans="2:23" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
-        <v>97</v>
-      </c>
-      <c r="C41" s="12"/>
+        <v>96</v>
+      </c>
+      <c r="C41" s="16"/>
       <c r="D41" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E41" s="6">
         <v>48</v>
@@ -2837,7 +2848,7 @@
         <v>90</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>17</v>
@@ -2845,50 +2856,24 @@
       <c r="L41" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="M41" s="16"/>
-      <c r="N41" s="16"/>
-      <c r="O41" s="16"/>
-      <c r="P41" s="16"/>
-      <c r="Q41" s="16"/>
-    </row>
-    <row r="42" spans="2:23" ht="20" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="43" spans="2:23" ht="20" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="44" spans="2:23" ht="20" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="45" spans="2:23" ht="20" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="46" spans="2:23" ht="20" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="47" spans="2:23" ht="20" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="48" spans="2:23" ht="20" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="49" ht="20" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="50" ht="20" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="51" ht="20" customHeight="1" x14ac:dyDescent="0.45"/>
+      <c r="M41" s="14"/>
+      <c r="N41" s="14"/>
+      <c r="O41" s="14"/>
+      <c r="P41" s="14"/>
+      <c r="Q41" s="14"/>
+    </row>
+    <row r="42" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="43" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="45" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="46" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="48" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="Q29:Q35"/>
-    <mergeCell ref="Q36:Q41"/>
-    <mergeCell ref="O29:O35"/>
-    <mergeCell ref="P29:P35"/>
-    <mergeCell ref="M36:M41"/>
-    <mergeCell ref="N36:N41"/>
-    <mergeCell ref="O36:O41"/>
-    <mergeCell ref="P36:P41"/>
-    <mergeCell ref="M29:M35"/>
-    <mergeCell ref="N29:N35"/>
-    <mergeCell ref="Z19:AA19"/>
-    <mergeCell ref="AG29:AG30"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="X14:Y14"/>
-    <mergeCell ref="Z8:AA8"/>
-    <mergeCell ref="Z9:AA9"/>
-    <mergeCell ref="Z10:AA10"/>
-    <mergeCell ref="Z11:AA11"/>
-    <mergeCell ref="Z12:AA12"/>
-    <mergeCell ref="X5:AA5"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="Z7:AA7"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="X9:Y9"/>
     <mergeCell ref="C29:C35"/>
     <mergeCell ref="C36:C41"/>
     <mergeCell ref="X6:Y6"/>
@@ -2905,6 +2890,32 @@
     <mergeCell ref="X11:Y11"/>
     <mergeCell ref="X12:Y12"/>
     <mergeCell ref="X13:Y13"/>
+    <mergeCell ref="X5:AA5"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="Z7:AA7"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="X9:Y9"/>
+    <mergeCell ref="X14:Y14"/>
+    <mergeCell ref="Z8:AA8"/>
+    <mergeCell ref="Z9:AA9"/>
+    <mergeCell ref="Z10:AA10"/>
+    <mergeCell ref="Z11:AA11"/>
+    <mergeCell ref="Z12:AA12"/>
+    <mergeCell ref="Z19:AA19"/>
+    <mergeCell ref="AG29:AG30"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="Q29:Q35"/>
+    <mergeCell ref="Q36:Q41"/>
+    <mergeCell ref="O29:O35"/>
+    <mergeCell ref="P29:P35"/>
+    <mergeCell ref="M36:M41"/>
+    <mergeCell ref="N36:N41"/>
+    <mergeCell ref="O36:O41"/>
+    <mergeCell ref="P36:P41"/>
+    <mergeCell ref="M29:M35"/>
+    <mergeCell ref="N29:N35"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>

--- a/기획/직업별 능력치_250515.xlsx
+++ b/기획/직업별 능력치_250515.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\typar\Desktop\storage\기획\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B8F978-293D-4572-9B0E-5F2C8FB3CBCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A47B48E-6315-4CED-9395-12B92F38FE5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16457" yWindow="-9017" windowWidth="18514" windowHeight="16157" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="107">
   <si>
     <t>최저 체력</t>
   </si>
@@ -351,6 +351,10 @@
   </si>
   <si>
     <t>30-(30*방어력)/100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -504,7 +508,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -541,6 +545,15 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -550,14 +563,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -915,7 +922,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B2:AH51"/>
+  <dimension ref="A2:AH51"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.875" customWidth="1"/>
@@ -955,12 +962,12 @@
       <c r="K5" t="s">
         <v>86</v>
       </c>
-      <c r="X5" s="15" t="s">
+      <c r="X5" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="Y5" s="15"/>
-      <c r="Z5" s="15"/>
-      <c r="AA5" s="15"/>
+      <c r="Y5" s="14"/>
+      <c r="Z5" s="14"/>
+      <c r="AA5" s="14"/>
       <c r="AB5" s="1" t="s">
         <v>13</v>
       </c>
@@ -1002,14 +1009,14 @@
       </c>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
-      <c r="X6" s="17" t="s">
+      <c r="X6" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="Y6" s="15"/>
-      <c r="Z6" s="15" t="s">
+      <c r="Y6" s="14"/>
+      <c r="Z6" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="AA6" s="15"/>
+      <c r="AA6" s="14"/>
       <c r="AB6" s="1" t="s">
         <v>18</v>
       </c>
@@ -1068,14 +1075,14 @@
       <c r="V7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="X7" s="15" t="s">
+      <c r="X7" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="Y7" s="15"/>
-      <c r="Z7" s="15" t="s">
+      <c r="Y7" s="14"/>
+      <c r="Z7" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="AA7" s="15"/>
+      <c r="AA7" s="14"/>
       <c r="AC7" s="1"/>
     </row>
     <row r="8" spans="2:29" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1139,16 +1146,16 @@
         <f>U8-(N24*2)</f>
         <v>74</v>
       </c>
-      <c r="X8" s="15">
+      <c r="X8" s="14">
         <f t="shared" ref="X8:X19" si="1">30-(30*O8)/100</f>
         <v>26.4</v>
       </c>
-      <c r="Y8" s="15"/>
-      <c r="Z8" s="15">
+      <c r="Y8" s="14"/>
+      <c r="Z8" s="14">
         <f t="shared" ref="Z8:Z19" si="2">30-P8</f>
         <v>15</v>
       </c>
-      <c r="AA8" s="15"/>
+      <c r="AA8" s="14"/>
       <c r="AB8" s="1">
         <f t="shared" ref="AB8:AB19" si="3">95-Q8*3</f>
         <v>92</v>
@@ -1219,16 +1226,16 @@
         <f>U9-(N24*2)</f>
         <v>79</v>
       </c>
-      <c r="X9" s="15">
+      <c r="X9" s="14">
         <f t="shared" si="1"/>
         <v>28.2</v>
       </c>
-      <c r="Y9" s="15"/>
-      <c r="Z9" s="15">
+      <c r="Y9" s="14"/>
+      <c r="Z9" s="14">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="AA9" s="15"/>
+      <c r="AA9" s="14"/>
       <c r="AB9" s="1">
         <f t="shared" si="3"/>
         <v>89</v>
@@ -1299,16 +1306,16 @@
         <f>U10-(N24*2)</f>
         <v>65</v>
       </c>
-      <c r="X10" s="15">
+      <c r="X10" s="14">
         <f t="shared" si="1"/>
         <v>28.8</v>
       </c>
-      <c r="Y10" s="15"/>
-      <c r="Z10" s="15">
+      <c r="Y10" s="14"/>
+      <c r="Z10" s="14">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="AA10" s="15"/>
+      <c r="AA10" s="14"/>
       <c r="AB10" s="1">
         <f t="shared" si="3"/>
         <v>74</v>
@@ -1379,16 +1386,16 @@
         <f>U11-(N24*2)</f>
         <v>71</v>
       </c>
-      <c r="X11" s="15">
+      <c r="X11" s="14">
         <f t="shared" si="1"/>
         <v>25.5</v>
       </c>
-      <c r="Y11" s="15"/>
-      <c r="Z11" s="15">
+      <c r="Y11" s="14"/>
+      <c r="Z11" s="14">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="AA11" s="15"/>
+      <c r="AA11" s="14"/>
       <c r="AB11" s="1">
         <f t="shared" si="3"/>
         <v>80</v>
@@ -1459,16 +1466,16 @@
         <f>U12-(N24*2)</f>
         <v>55</v>
       </c>
-      <c r="X12" s="15">
+      <c r="X12" s="14">
         <f t="shared" si="1"/>
         <v>28.8</v>
       </c>
-      <c r="Y12" s="15"/>
-      <c r="Z12" s="15">
+      <c r="Y12" s="14"/>
+      <c r="Z12" s="14">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="AA12" s="15"/>
+      <c r="AA12" s="14"/>
       <c r="AB12" s="1">
         <f t="shared" si="3"/>
         <v>71</v>
@@ -1539,16 +1546,16 @@
         <f>U13-(N24*2)</f>
         <v>59</v>
       </c>
-      <c r="X13" s="15">
+      <c r="X13" s="14">
         <f t="shared" si="1"/>
         <v>27.9</v>
       </c>
-      <c r="Y13" s="15"/>
-      <c r="Z13" s="15">
+      <c r="Y13" s="14"/>
+      <c r="Z13" s="14">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="AA13" s="15"/>
+      <c r="AA13" s="14"/>
       <c r="AB13" s="1">
         <f t="shared" si="3"/>
         <v>77</v>
@@ -1619,16 +1626,16 @@
         <f>U14-(N24*2)</f>
         <v>51</v>
       </c>
-      <c r="X14" s="15">
+      <c r="X14" s="14">
         <f t="shared" si="1"/>
         <v>29.1</v>
       </c>
-      <c r="Y14" s="15"/>
-      <c r="Z14" s="15">
+      <c r="Y14" s="14"/>
+      <c r="Z14" s="14">
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="AA14" s="15"/>
+      <c r="AA14" s="14"/>
       <c r="AB14" s="1">
         <f t="shared" si="3"/>
         <v>86</v>
@@ -1699,16 +1706,16 @@
         <f>U15-(N24*2)</f>
         <v>60</v>
       </c>
-      <c r="X15" s="15">
+      <c r="X15" s="14">
         <f t="shared" si="1"/>
         <v>29.1</v>
       </c>
-      <c r="Y15" s="15"/>
-      <c r="Z15" s="15">
+      <c r="Y15" s="14"/>
+      <c r="Z15" s="14">
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="AA15" s="15"/>
+      <c r="AA15" s="14"/>
       <c r="AB15" s="1">
         <f t="shared" si="3"/>
         <v>83</v>
@@ -1779,16 +1786,16 @@
         <f>U16-(N24*2)</f>
         <v>61</v>
       </c>
-      <c r="X16" s="15">
+      <c r="X16" s="14">
         <f t="shared" si="1"/>
         <v>28.5</v>
       </c>
-      <c r="Y16" s="15"/>
-      <c r="Z16" s="15">
+      <c r="Y16" s="14"/>
+      <c r="Z16" s="14">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="AA16" s="15"/>
+      <c r="AA16" s="14"/>
       <c r="AB16" s="1">
         <f t="shared" si="3"/>
         <v>86</v>
@@ -1798,7 +1805,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="2:34" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:34" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C17" s="2" t="s">
         <v>9</v>
       </c>
@@ -1859,16 +1866,16 @@
         <f>U17-(N24*2)</f>
         <v>57</v>
       </c>
-      <c r="X17" s="15">
+      <c r="X17" s="14">
         <f t="shared" si="1"/>
         <v>29.1</v>
       </c>
-      <c r="Y17" s="15"/>
-      <c r="Z17" s="15">
+      <c r="Y17" s="14"/>
+      <c r="Z17" s="14">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="AA17" s="15"/>
+      <c r="AA17" s="14"/>
       <c r="AB17" s="1">
         <f t="shared" si="3"/>
         <v>65</v>
@@ -1878,7 +1885,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="2:34" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:34" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C18" s="2" t="s">
         <v>2</v>
       </c>
@@ -1939,16 +1946,16 @@
         <f>U18-(N24*2)</f>
         <v>44</v>
       </c>
-      <c r="X18" s="15">
+      <c r="X18" s="14">
         <f t="shared" si="1"/>
         <v>29.4</v>
       </c>
-      <c r="Y18" s="15"/>
-      <c r="Z18" s="15">
+      <c r="Y18" s="14"/>
+      <c r="Z18" s="14">
         <f t="shared" si="2"/>
         <v>26</v>
       </c>
-      <c r="AA18" s="15"/>
+      <c r="AA18" s="14"/>
       <c r="AB18" s="1">
         <f t="shared" si="3"/>
         <v>92</v>
@@ -1958,7 +1965,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="2:34" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:34" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C19" s="2" t="s">
         <v>58</v>
       </c>
@@ -2019,16 +2026,16 @@
         <f>U19-(N24*2)</f>
         <v>49</v>
       </c>
-      <c r="X19" s="15">
+      <c r="X19" s="14">
         <f t="shared" si="1"/>
         <v>29.4</v>
       </c>
-      <c r="Y19" s="15"/>
-      <c r="Z19" s="15">
+      <c r="Y19" s="14"/>
+      <c r="Z19" s="14">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="AA19" s="15"/>
+      <c r="AA19" s="14"/>
       <c r="AB19" s="1">
         <f t="shared" si="3"/>
         <v>92</v>
@@ -2038,7 +2045,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="2:34" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:34" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
         <v>90</v>
       </c>
@@ -2095,7 +2102,7 @@
       <c r="U20" s="2"/>
       <c r="V20" s="2"/>
     </row>
-    <row r="21" spans="2:34" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:34" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C21" s="2" t="s">
         <v>81</v>
       </c>
@@ -2149,10 +2156,10 @@
       <c r="U21" s="2"/>
       <c r="V21" s="2"/>
     </row>
-    <row r="22" spans="2:34" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:34" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D22" s="4"/>
     </row>
-    <row r="23" spans="2:34" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.3">
       <c r="L23" t="s">
         <v>36</v>
       </c>
@@ -2176,7 +2183,7 @@
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
     </row>
-    <row r="24" spans="2:34" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.3">
       <c r="M24" s="1" t="s">
         <v>101</v>
       </c>
@@ -2197,7 +2204,7 @@
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
     </row>
-    <row r="25" spans="2:34" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:34" x14ac:dyDescent="0.3">
       <c r="M25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
@@ -2208,7 +2215,7 @@
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
     </row>
-    <row r="26" spans="2:34" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:34" x14ac:dyDescent="0.3">
       <c r="M26" s="1"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
@@ -2219,7 +2226,7 @@
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
     </row>
-    <row r="27" spans="2:34" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.3">
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
@@ -2229,7 +2236,10 @@
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
     </row>
-    <row r="28" spans="2:34" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:34" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="18" t="s">
+        <v>106</v>
+      </c>
       <c r="C28" s="1"/>
       <c r="D28" s="2" t="s">
         <v>56</v>
@@ -2280,11 +2290,14 @@
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
     </row>
-    <row r="29" spans="2:34" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:34" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>2</v>
+      </c>
       <c r="B29" t="s">
         <v>33</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="12" t="s">
         <v>54</v>
       </c>
       <c r="D29" s="5" t="s">
@@ -2314,23 +2327,23 @@
       <c r="L29" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="M29" s="12">
+      <c r="M29" s="15">
         <f>ROUND(AVERAGE(E29:E35),1)</f>
         <v>33.4</v>
       </c>
-      <c r="N29" s="12">
+      <c r="N29" s="15">
         <f>ROUND(AVERAGE(F29:F35),1)</f>
         <v>5</v>
       </c>
-      <c r="O29" s="12">
+      <c r="O29" s="15">
         <f>ROUND(AVERAGE(G29:G35),1)</f>
         <v>2.1</v>
       </c>
-      <c r="P29" s="12">
+      <c r="P29" s="15">
         <f>ROUND(AVERAGE(H29:H35),1)</f>
         <v>4.4000000000000004</v>
       </c>
-      <c r="Q29" s="12">
+      <c r="Q29" s="15">
         <f>ROUND(AVERAGE(I29:I35),1)</f>
         <v>95</v>
       </c>
@@ -2340,18 +2353,21 @@
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
-      <c r="AG29" s="15" t="s">
+      <c r="AG29" s="14" t="s">
         <v>72</v>
       </c>
       <c r="AH29" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="2:34" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:34" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>1</v>
+      </c>
       <c r="B30" t="s">
         <v>99</v>
       </c>
-      <c r="C30" s="16"/>
+      <c r="C30" s="12"/>
       <c r="D30" s="2" t="s">
         <v>59</v>
       </c>
@@ -2377,27 +2393,30 @@
         <v>23</v>
       </c>
       <c r="L30" s="2"/>
-      <c r="M30" s="13"/>
-      <c r="N30" s="13"/>
-      <c r="O30" s="13"/>
-      <c r="P30" s="13"/>
-      <c r="Q30" s="13"/>
+      <c r="M30" s="16"/>
+      <c r="N30" s="16"/>
+      <c r="O30" s="16"/>
+      <c r="P30" s="16"/>
+      <c r="Q30" s="16"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
-      <c r="AG30" s="15"/>
+      <c r="AG30" s="14"/>
       <c r="AH30" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="2:34" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:34" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>3</v>
+      </c>
       <c r="B31" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="16"/>
+      <c r="C31" s="12"/>
       <c r="D31" s="2" t="s">
         <v>68</v>
       </c>
@@ -2423,11 +2442,11 @@
         <v>27</v>
       </c>
       <c r="L31" s="2"/>
-      <c r="M31" s="13"/>
-      <c r="N31" s="13"/>
-      <c r="O31" s="13"/>
-      <c r="P31" s="13"/>
-      <c r="Q31" s="13"/>
+      <c r="M31" s="16"/>
+      <c r="N31" s="16"/>
+      <c r="O31" s="16"/>
+      <c r="P31" s="16"/>
+      <c r="Q31" s="16"/>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
       <c r="T31" s="1"/>
@@ -2441,11 +2460,14 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="32" spans="2:34" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:34" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>4</v>
+      </c>
       <c r="B32" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="16"/>
+      <c r="C32" s="12"/>
       <c r="D32" s="6" t="s">
         <v>69</v>
       </c>
@@ -2473,11 +2495,11 @@
       <c r="L32" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="M32" s="13"/>
-      <c r="N32" s="13"/>
-      <c r="O32" s="13"/>
-      <c r="P32" s="13"/>
-      <c r="Q32" s="13"/>
+      <c r="M32" s="16"/>
+      <c r="N32" s="16"/>
+      <c r="O32" s="16"/>
+      <c r="P32" s="16"/>
+      <c r="Q32" s="16"/>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
       <c r="T32" s="1"/>
@@ -2485,11 +2507,11 @@
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
     </row>
-    <row r="33" spans="2:23" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:23" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>98</v>
       </c>
-      <c r="C33" s="16"/>
+      <c r="C33" s="12"/>
       <c r="D33" s="7" t="s">
         <v>60</v>
       </c>
@@ -2515,11 +2537,11 @@
         <v>39</v>
       </c>
       <c r="L33" s="7"/>
-      <c r="M33" s="13"/>
-      <c r="N33" s="13"/>
-      <c r="O33" s="13"/>
-      <c r="P33" s="13"/>
-      <c r="Q33" s="13"/>
+      <c r="M33" s="16"/>
+      <c r="N33" s="16"/>
+      <c r="O33" s="16"/>
+      <c r="P33" s="16"/>
+      <c r="Q33" s="16"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
@@ -2527,11 +2549,11 @@
       <c r="V33" s="1"/>
       <c r="W33" s="1"/>
     </row>
-    <row r="34" spans="2:23" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:23" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>37</v>
       </c>
-      <c r="C34" s="16"/>
+      <c r="C34" s="12"/>
       <c r="D34" s="8" t="s">
         <v>78</v>
       </c>
@@ -2557,11 +2579,11 @@
         <v>35</v>
       </c>
       <c r="L34" s="8"/>
-      <c r="M34" s="13"/>
-      <c r="N34" s="13"/>
-      <c r="O34" s="13"/>
-      <c r="P34" s="13"/>
-      <c r="Q34" s="13"/>
+      <c r="M34" s="16"/>
+      <c r="N34" s="16"/>
+      <c r="O34" s="16"/>
+      <c r="P34" s="16"/>
+      <c r="Q34" s="16"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
@@ -2569,11 +2591,14 @@
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
     </row>
-    <row r="35" spans="2:23" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:23" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>5</v>
+      </c>
       <c r="B35" t="s">
         <v>29</v>
       </c>
-      <c r="C35" s="16"/>
+      <c r="C35" s="12"/>
       <c r="D35" s="8" t="s">
         <v>46</v>
       </c>
@@ -2601,11 +2626,11 @@
       <c r="L35" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="M35" s="14"/>
-      <c r="N35" s="14"/>
-      <c r="O35" s="14"/>
-      <c r="P35" s="14"/>
-      <c r="Q35" s="14"/>
+      <c r="M35" s="17"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="17"/>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
       <c r="T35" s="1"/>
@@ -2613,11 +2638,11 @@
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
     </row>
-    <row r="36" spans="2:23" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:23" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>30</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C36" s="12" t="s">
         <v>55</v>
       </c>
       <c r="D36" s="5" t="s">
@@ -2647,23 +2672,23 @@
       <c r="L36" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="M36" s="12">
+      <c r="M36" s="15">
         <f>ROUND(AVERAGE(E36:E41),1)</f>
         <v>42.5</v>
       </c>
-      <c r="N36" s="12">
+      <c r="N36" s="15">
         <f t="shared" ref="N36:Q36" si="12">ROUND(AVERAGE(F36:F41),1)</f>
         <v>7.5</v>
       </c>
-      <c r="O36" s="12">
+      <c r="O36" s="15">
         <f t="shared" si="12"/>
         <v>4.2</v>
       </c>
-      <c r="P36" s="12">
+      <c r="P36" s="15">
         <f t="shared" si="12"/>
         <v>4.5</v>
       </c>
-      <c r="Q36" s="12">
+      <c r="Q36" s="15">
         <f t="shared" si="12"/>
         <v>95.8</v>
       </c>
@@ -2674,11 +2699,11 @@
       <c r="V36" s="1"/>
       <c r="W36" s="1"/>
     </row>
-    <row r="37" spans="2:23" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:23" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>31</v>
       </c>
-      <c r="C37" s="16"/>
+      <c r="C37" s="12"/>
       <c r="D37" s="2" t="s">
         <v>88</v>
       </c>
@@ -2706,17 +2731,17 @@
       <c r="L37" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M37" s="13"/>
-      <c r="N37" s="13"/>
-      <c r="O37" s="13"/>
-      <c r="P37" s="13"/>
-      <c r="Q37" s="13"/>
-    </row>
-    <row r="38" spans="2:23" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M37" s="16"/>
+      <c r="N37" s="16"/>
+      <c r="O37" s="16"/>
+      <c r="P37" s="16"/>
+      <c r="Q37" s="16"/>
+    </row>
+    <row r="38" spans="1:23" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>34</v>
       </c>
-      <c r="C38" s="16"/>
+      <c r="C38" s="12"/>
       <c r="D38" s="6" t="s">
         <v>87</v>
       </c>
@@ -2744,17 +2769,20 @@
       <c r="L38" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="M38" s="13"/>
-      <c r="N38" s="13"/>
-      <c r="O38" s="13"/>
-      <c r="P38" s="13"/>
-      <c r="Q38" s="13"/>
-    </row>
-    <row r="39" spans="2:23" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M38" s="16"/>
+      <c r="N38" s="16"/>
+      <c r="O38" s="16"/>
+      <c r="P38" s="16"/>
+      <c r="Q38" s="16"/>
+    </row>
+    <row r="39" spans="1:23" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>6</v>
+      </c>
       <c r="B39" t="s">
         <v>102</v>
       </c>
-      <c r="C39" s="16"/>
+      <c r="C39" s="12"/>
       <c r="D39" s="8" t="s">
         <v>49</v>
       </c>
@@ -2780,17 +2808,17 @@
         <v>41</v>
       </c>
       <c r="L39" s="8"/>
-      <c r="M39" s="13"/>
-      <c r="N39" s="13"/>
-      <c r="O39" s="13"/>
-      <c r="P39" s="13"/>
-      <c r="Q39" s="13"/>
-    </row>
-    <row r="40" spans="2:23" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M39" s="16"/>
+      <c r="N39" s="16"/>
+      <c r="O39" s="16"/>
+      <c r="P39" s="16"/>
+      <c r="Q39" s="16"/>
+    </row>
+    <row r="40" spans="1:23" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>71</v>
       </c>
-      <c r="C40" s="16"/>
+      <c r="C40" s="12"/>
       <c r="D40" s="5" t="s">
         <v>64</v>
       </c>
@@ -2818,17 +2846,17 @@
       <c r="L40" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="M40" s="13"/>
-      <c r="N40" s="13"/>
-      <c r="O40" s="13"/>
-      <c r="P40" s="13"/>
-      <c r="Q40" s="13"/>
-    </row>
-    <row r="41" spans="2:23" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M40" s="16"/>
+      <c r="N40" s="16"/>
+      <c r="O40" s="16"/>
+      <c r="P40" s="16"/>
+      <c r="Q40" s="16"/>
+    </row>
+    <row r="41" spans="1:23" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>96</v>
       </c>
-      <c r="C41" s="16"/>
+      <c r="C41" s="12"/>
       <c r="D41" s="6" t="s">
         <v>51</v>
       </c>
@@ -2856,24 +2884,50 @@
       <c r="L41" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="M41" s="14"/>
-      <c r="N41" s="14"/>
-      <c r="O41" s="14"/>
-      <c r="P41" s="14"/>
-      <c r="Q41" s="14"/>
-    </row>
-    <row r="42" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="43" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="44" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="45" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="46" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="47" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="48" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="M41" s="17"/>
+      <c r="N41" s="17"/>
+      <c r="O41" s="17"/>
+      <c r="P41" s="17"/>
+      <c r="Q41" s="17"/>
+    </row>
+    <row r="42" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="43" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="45" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="46" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="48" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="Q29:Q35"/>
+    <mergeCell ref="Q36:Q41"/>
+    <mergeCell ref="O29:O35"/>
+    <mergeCell ref="P29:P35"/>
+    <mergeCell ref="M36:M41"/>
+    <mergeCell ref="N36:N41"/>
+    <mergeCell ref="O36:O41"/>
+    <mergeCell ref="P36:P41"/>
+    <mergeCell ref="M29:M35"/>
+    <mergeCell ref="N29:N35"/>
+    <mergeCell ref="Z19:AA19"/>
+    <mergeCell ref="AG29:AG30"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="X14:Y14"/>
+    <mergeCell ref="Z8:AA8"/>
+    <mergeCell ref="Z9:AA9"/>
+    <mergeCell ref="Z10:AA10"/>
+    <mergeCell ref="Z11:AA11"/>
+    <mergeCell ref="Z12:AA12"/>
+    <mergeCell ref="X5:AA5"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="Z7:AA7"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="X9:Y9"/>
     <mergeCell ref="C29:C35"/>
     <mergeCell ref="C36:C41"/>
     <mergeCell ref="X6:Y6"/>
@@ -2890,32 +2944,6 @@
     <mergeCell ref="X11:Y11"/>
     <mergeCell ref="X12:Y12"/>
     <mergeCell ref="X13:Y13"/>
-    <mergeCell ref="X5:AA5"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="Z7:AA7"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="X9:Y9"/>
-    <mergeCell ref="X14:Y14"/>
-    <mergeCell ref="Z8:AA8"/>
-    <mergeCell ref="Z9:AA9"/>
-    <mergeCell ref="Z10:AA10"/>
-    <mergeCell ref="Z11:AA11"/>
-    <mergeCell ref="Z12:AA12"/>
-    <mergeCell ref="Z19:AA19"/>
-    <mergeCell ref="AG29:AG30"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="Q29:Q35"/>
-    <mergeCell ref="Q36:Q41"/>
-    <mergeCell ref="O29:O35"/>
-    <mergeCell ref="P29:P35"/>
-    <mergeCell ref="M36:M41"/>
-    <mergeCell ref="N36:N41"/>
-    <mergeCell ref="O36:O41"/>
-    <mergeCell ref="P36:P41"/>
-    <mergeCell ref="M29:M35"/>
-    <mergeCell ref="N29:N35"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
